--- a/output/pdf_financials_xlsx/BBB.xlsx
+++ b/output/pdf_financials_xlsx/BBB.xlsx
@@ -5073,40 +5073,40 @@
         <v>0.475379</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>0.730622</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>1.240117</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>1.347519</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>1.3524</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>3.568762</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>4.449429</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>5.487859</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>7.782579</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>10.839406</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>11.29955</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>0</v>
+        <v>12.324322</v>
       </c>
       <c r="O92" s="3" t="n">
-        <v>0</v>
+        <v>12.462942</v>
       </c>
     </row>
     <row r="93">
@@ -6381,7 +6381,7 @@
         <v>0</v>
       </c>
       <c r="N118" s="3" t="n">
-        <v>0</v>
+        <v>0.345266</v>
       </c>
       <c r="O118" s="1" t="inlineStr">
         <is>
@@ -8898,7 +8898,11 @@
           <t>Reserves (Note 13(d))</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr"/>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E21" t="inlineStr">
         <is>
           <t>-</t>
@@ -10296,7 +10300,11 @@
           <t>Reserves (Note 12(d))</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr"/>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E38" t="inlineStr">
         <is>
           <t>-</t>
@@ -11582,7 +11590,11 @@
           <t>Reserves (note 11(d))</t>
         </is>
       </c>
-      <c r="D53" t="inlineStr"/>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E53" t="inlineStr">
         <is>
           <t>-</t>
@@ -14632,7 +14644,11 @@
           <t>Advance on exploration and evaluation expenditures</t>
         </is>
       </c>
-      <c r="D90" t="inlineStr"/>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E90" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/BBB.xlsx
+++ b/output/pdf_financials_xlsx/BBB.xlsx
@@ -967,31 +967,31 @@
         <v>0</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>0.032781</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>0.019035</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>0.014396</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>0.028944</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0</v>
+        <v>0.028994</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0</v>
+        <v>0.037743</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0</v>
+        <v>0.001255</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>0</v>
+        <v>0.470599</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>0</v>
+        <v>0.617818</v>
       </c>
       <c r="O12" s="1" t="inlineStr">
         <is>
@@ -1784,31 +1784,31 @@
         <v>-3.393662</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-1.879318</v>
+        <v>-1.912099</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-0.689906</v>
+        <v>-0.708941</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>-4.683434</v>
+        <v>-4.69783</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>-3.9787</v>
+        <v>-4.007644</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>-5.118008</v>
+        <v>-5.147002</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>-7.712888</v>
+        <v>-7.750631</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>-12.6038</v>
+        <v>-12.605055</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>-16.966994</v>
+        <v>-17.437593</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>-13.645609</v>
+        <v>-14.263427</v>
       </c>
       <c r="O27" s="1" t="inlineStr">
         <is>
@@ -1886,31 +1886,31 @@
         <v>-3.393662</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-1.879318</v>
+        <v>-1.912099</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-0.689906</v>
+        <v>-0.708941</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-4.683434</v>
+        <v>-4.69783</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-3.9787</v>
+        <v>-4.007644</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>-5.118008</v>
+        <v>-5.147002</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-7.712888</v>
+        <v>-7.750631</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>-12.6038</v>
+        <v>-12.605055</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>-16.966994</v>
+        <v>-17.437593</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>-13.645609</v>
+        <v>-14.263427</v>
       </c>
       <c r="O29" s="1" t="inlineStr">
         <is>
@@ -2155,28 +2155,28 @@
         <v>0.474881</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>4.336565</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>2.664018</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>1.383153</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>5.842871</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>7.542275</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>5.533109</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>7.204869</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>3.848109</v>
       </c>
     </row>
     <row r="35">
@@ -2253,28 +2253,28 @@
         <v>0.474881</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>4.336565</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>2.664018</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>1.383153</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>5.842871</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0.07000000000000001</v>
+        <v>7.612275</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>5.533109</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>7.204869</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0.7126980000000001</v>
+        <v>4.560807</v>
       </c>
     </row>
     <row r="37">
@@ -2841,28 +2841,28 @@
         <v>0.018322</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>4.443427</v>
+        <v>0.106862</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>2.751779</v>
+        <v>0.08776100000000001</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>1.491083</v>
+        <v>0.10793</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>5.959251</v>
+        <v>0.11638</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>7.96838</v>
+        <v>0.426105</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>5.74506</v>
+        <v>0.211951</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>7.411226</v>
+        <v>0.206357</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>4.109529</v>
+        <v>0.26142</v>
       </c>
     </row>
     <row r="49">
@@ -7422,7 +7422,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -26866,7 +26866,7 @@
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E237" t="inlineStr">
@@ -29256,7 +29256,7 @@
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E265" t="inlineStr">
@@ -38462,7 +38462,7 @@
       </c>
       <c r="D374" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E374" t="inlineStr">
